--- a/teacher data.xlsx
+++ b/teacher data.xlsx
@@ -436,7 +436,7 @@
         <v>8100610943</v>
       </c>
       <c r="F2" t="str">
-        <v>ap2446961@gmail.com</v>
+        <v>chak.ayantika@gmail.com</v>
       </c>
     </row>
     <row r="3">

--- a/teacher data.xlsx
+++ b/teacher data.xlsx
@@ -436,7 +436,7 @@
         <v>8100610943</v>
       </c>
       <c r="F2" t="str">
-        <v>chak.ayantika@gmail.com</v>
+        <v>ap2446961@gmail.com</v>
       </c>
     </row>
     <row r="3">
